--- a/SubClase/MDC_SubClase.xlsx
+++ b/SubClase/MDC_SubClase.xlsx
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="2">
-        <v>4.417173060056014</v>
+        <v>4.417173060056015</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1530,13 +1530,13 @@
         <v>3.26</v>
       </c>
       <c r="C52" s="2">
-        <v>104.4746336396601</v>
+        <v>104.4746336396602</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E52" s="2">
-        <v>3.405873056652921</v>
+        <v>3.405873056652922</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1547,13 +1547,13 @@
         <v>4.83</v>
       </c>
       <c r="C53" s="2">
-        <v>102.8004794290012</v>
+        <v>102.8004794290011</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E53" s="2">
-        <v>4.965263156420757</v>
+        <v>4.965263156420756</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1972,7 +1972,7 @@
         <v>13.94</v>
       </c>
       <c r="C78" s="2">
-        <v>114.8194712876382</v>
+        <v>114.8194712876383</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>6</v>
